--- a/data/harvest_program_2025_26.xlsx
+++ b/data/harvest_program_2025_26.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
   <si>
     <t>DATE</t>
   </si>
@@ -586,19 +586,9 @@
             <v>N41</v>
           </cell>
         </row>
-        <row r="14">
-          <cell r="C14" t="str">
-            <v>97F1692</v>
-          </cell>
-        </row>
         <row r="15">
           <cell r="C15" t="str">
             <v>R570</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="C16" t="str">
-            <v>N41</v>
           </cell>
         </row>
         <row r="17">
@@ -607,12 +597,12 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1535,9 +1525,8 @@
       <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="11" t="str">
-        <f>'[1]ESTATE 2025'!C14</f>
-        <v>97F1692</v>
+      <c r="C17" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>73</v>
@@ -1613,9 +1602,8 @@
       <c r="B19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="11" t="str">
-        <f>'[1]ESTATE 2025'!C16</f>
-        <v>N41</v>
+      <c r="C19" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>69</v>
@@ -1844,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>70</v>
@@ -2186,7 +2174,7 @@
         <v>23</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>80</v>
@@ -2262,7 +2250,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>81</v>
